--- a/marebuis_vol2_f.xlsx
+++ b/marebuis_vol2_f.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c281a82ac62a8fe2/デスクトップ/研究Ongo/MareBuis/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="653" documentId="11_1147F767884006CC70C5DF64F5012D16E1073E97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF6D373-8F1C-46A6-9B42-AC8A774B55C9}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="11_1147F767884006CC70C5DF64F5012D16E1073E97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0143749-B397-46B0-B45D-650DF240D94F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +33,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -10662,6 +10657,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20900,7 +20896,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -23549,6 +23546,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>